--- a/ECB_skewness_lt.xlsx
+++ b/ECB_skewness_lt.xlsx
@@ -75,7 +75,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -130,13 +130,13 @@
         <v>0.88727086782455444</v>
       </c>
       <c r="C5" s="2">
-        <v>0.77241760492324829</v>
+        <v>0.76613938808441162</v>
       </c>
       <c r="D5" s="2">
         <v>0.75177186727523804</v>
       </c>
       <c r="E5" s="2">
-        <v>0.62814927101135254</v>
+        <v>0.62107253074645996</v>
       </c>
     </row>
     <row r="6">
@@ -147,13 +147,13 @@
         <v>0.48910319805145264</v>
       </c>
       <c r="C6" s="2">
-        <v>0.35116145014762878</v>
+        <v>0.34337744116783142</v>
       </c>
       <c r="D6" s="2">
         <v>0.7444491982460022</v>
       </c>
       <c r="E6" s="2">
-        <v>0.63088101148605347</v>
+        <v>0.62436175346374512</v>
       </c>
     </row>
     <row r="7">
@@ -164,13 +164,13 @@
         <v>0.66977864503860474</v>
       </c>
       <c r="C7" s="2">
-        <v>0.56391721963882446</v>
+        <v>0.55596286058425903</v>
       </c>
       <c r="D7" s="2">
         <v>0.76829540729522705</v>
       </c>
       <c r="E7" s="2">
-        <v>0.66285288333892822</v>
+        <v>0.65619611740112305</v>
       </c>
     </row>
     <row r="8">
@@ -181,13 +181,13 @@
         <v>0.67671900987625122</v>
       </c>
       <c r="C8" s="2">
-        <v>0.51864200830459595</v>
+        <v>0.51213103532791138</v>
       </c>
       <c r="D8" s="2">
         <v>0.8611454963684082</v>
       </c>
       <c r="E8" s="2">
-        <v>0.75899547338485718</v>
+        <v>0.75299376249313354</v>
       </c>
     </row>
     <row r="9">
@@ -198,13 +198,13 @@
         <v>1.0359877347946167</v>
       </c>
       <c r="C9" s="2">
-        <v>0.93460792303085327</v>
+        <v>0.92775201797485352</v>
       </c>
       <c r="D9" s="2">
         <v>0.86181104183197021</v>
       </c>
       <c r="E9" s="2">
-        <v>0.75947266817092896</v>
+        <v>0.75376367568969727</v>
       </c>
     </row>
     <row r="10">
@@ -215,13 +215,13 @@
         <v>0.70783579349517822</v>
       </c>
       <c r="C10" s="2">
-        <v>0.64454001188278198</v>
+        <v>0.6408076286315918</v>
       </c>
       <c r="D10" s="2">
         <v>0.78314322233200073</v>
       </c>
       <c r="E10" s="2">
-        <v>0.67708730697631836</v>
+        <v>0.67181164026260376</v>
       </c>
     </row>
     <row r="11">
@@ -232,13 +232,13 @@
         <v>0.91137278079986572</v>
       </c>
       <c r="C11" s="2">
-        <v>0.85468411445617676</v>
+        <v>0.84720253944396973</v>
       </c>
       <c r="D11" s="2">
         <v>0.79346698522567749</v>
       </c>
       <c r="E11" s="2">
-        <v>0.69506186246871948</v>
+        <v>0.6898268461227417</v>
       </c>
     </row>
     <row r="12">
@@ -249,13 +249,13 @@
         <v>1.5110960006713867</v>
       </c>
       <c r="C12" s="2">
-        <v>1.4319933652877808</v>
+        <v>1.4305770397186279</v>
       </c>
       <c r="D12" s="2">
         <v>0.79477423429489136</v>
       </c>
       <c r="E12" s="2">
-        <v>0.69977849721908569</v>
+        <v>0.6946941614151001</v>
       </c>
     </row>
     <row r="13">
@@ -266,13 +266,13 @@
         <v>0.86713510751724243</v>
       </c>
       <c r="C13" s="2">
-        <v>0.7632904052734375</v>
+        <v>0.75992310047149658</v>
       </c>
       <c r="D13" s="2">
         <v>0.78524363040924072</v>
       </c>
       <c r="E13" s="2">
-        <v>0.70903778076171875</v>
+        <v>0.70465153455734253</v>
       </c>
     </row>
     <row r="14">
@@ -283,13 +283,13 @@
         <v>0.1792607456445694</v>
       </c>
       <c r="C14" s="2">
-        <v>0.030949430540204048</v>
+        <v>0.028570838272571564</v>
       </c>
       <c r="D14" s="2">
         <v>0.7518150806427002</v>
       </c>
       <c r="E14" s="2">
-        <v>0.68135523796081543</v>
+        <v>0.6775173544883728</v>
       </c>
     </row>
     <row r="15">
@@ -300,13 +300,13 @@
         <v>0.58201706409454346</v>
       </c>
       <c r="C15" s="2">
-        <v>0.5129324197769165</v>
+        <v>0.50551456212997437</v>
       </c>
       <c r="D15" s="2">
         <v>0.74020195007324219</v>
       </c>
       <c r="E15" s="2">
-        <v>0.67107510566711426</v>
+        <v>0.66761958599090576</v>
       </c>
     </row>
     <row r="16">
@@ -317,13 +317,13 @@
         <v>0.68154394626617432</v>
       </c>
       <c r="C16" s="2">
-        <v>0.60636657476425171</v>
+        <v>0.59976887702941895</v>
       </c>
       <c r="D16" s="2">
         <v>0.70064973831176758</v>
       </c>
       <c r="E16" s="2">
-        <v>0.6263502836227417</v>
+        <v>0.62284260988235474</v>
       </c>
     </row>
     <row r="17">
@@ -334,13 +334,13 @@
         <v>0.59094357490539551</v>
       </c>
       <c r="C17" s="2">
-        <v>0.60197561979293823</v>
+        <v>0.60174727439880371</v>
       </c>
       <c r="D17" s="2">
         <v>0.6134495735168457</v>
       </c>
       <c r="E17" s="2">
-        <v>0.54420250654220581</v>
+        <v>0.54010295867919922</v>
       </c>
     </row>
     <row r="18">
@@ -351,13 +351,13 @@
         <v>0.73513048887252808</v>
       </c>
       <c r="C18" s="2">
-        <v>0.68546545505523682</v>
+        <v>0.68354415893554688</v>
       </c>
       <c r="D18" s="2">
         <v>0.56866580247879028</v>
       </c>
       <c r="E18" s="2">
-        <v>0.50154620409011841</v>
+        <v>0.49686133861541748</v>
       </c>
     </row>
     <row r="19">
@@ -368,13 +368,13 @@
         <v>0.60331767797470093</v>
       </c>
       <c r="C19" s="2">
-        <v>0.55201870203018188</v>
+        <v>0.55172806978225708</v>
       </c>
       <c r="D19" s="2">
         <v>0.63189274072647095</v>
       </c>
       <c r="E19" s="2">
-        <v>0.5723302960395813</v>
+        <v>0.56669443845748901</v>
       </c>
     </row>
     <row r="20">
@@ -385,13 +385,13 @@
         <v>0.55540323257446289</v>
       </c>
       <c r="C20" s="2">
-        <v>0.45216038823127747</v>
+        <v>0.44420954585075378</v>
       </c>
       <c r="D20" s="2">
         <v>0.63897275924682617</v>
       </c>
       <c r="E20" s="2">
-        <v>0.57996618747711182</v>
+        <v>0.57485854625701904</v>
       </c>
     </row>
     <row r="21">
@@ -402,13 +402,13 @@
         <v>0.72629457712173462</v>
       </c>
       <c r="C21" s="2">
-        <v>0.69266366958618164</v>
+        <v>0.6859203577041626</v>
       </c>
       <c r="D21" s="2">
         <v>0.61734813451766968</v>
       </c>
       <c r="E21" s="2">
-        <v>0.55501270294189453</v>
+        <v>0.54973608255386353</v>
       </c>
     </row>
     <row r="22">
@@ -419,13 +419,13 @@
         <v>0.4640810489654541</v>
       </c>
       <c r="C22" s="2">
-        <v>0.37938377261161804</v>
+        <v>0.37074831128120422</v>
       </c>
       <c r="D22" s="2">
         <v>0.55997765064239502</v>
       </c>
       <c r="E22" s="2">
-        <v>0.48392975330352783</v>
+        <v>0.47795864939689636</v>
       </c>
     </row>
     <row r="23">
@@ -436,13 +436,13 @@
         <v>0.7483028769493103</v>
       </c>
       <c r="C23" s="2">
-        <v>0.66800594329833984</v>
+        <v>0.65706890821456909</v>
       </c>
       <c r="D23" s="2">
         <v>0.50966250896453857</v>
       </c>
       <c r="E23" s="2">
-        <v>0.42876240611076355</v>
+        <v>0.42213362455368042</v>
       </c>
     </row>
     <row r="24">
@@ -453,13 +453,13 @@
         <v>0.64573764801025391</v>
       </c>
       <c r="C24" s="2">
-        <v>0.58165568113327026</v>
+        <v>0.57899153232574463</v>
       </c>
       <c r="D24" s="2">
         <v>0.44177782535552979</v>
       </c>
       <c r="E24" s="2">
-        <v>0.35514086484909058</v>
+        <v>0.34806305170059204</v>
       </c>
     </row>
     <row r="25">
@@ -470,13 +470,13 @@
         <v>0.48692196607589722</v>
       </c>
       <c r="C25" s="2">
-        <v>0.38178521394729614</v>
+        <v>0.3736664354801178</v>
       </c>
       <c r="D25" s="2">
         <v>0.38858711719512939</v>
       </c>
       <c r="E25" s="2">
-        <v>0.29685455560684204</v>
+        <v>0.28698793053627014</v>
       </c>
     </row>
     <row r="26">
@@ -487,13 +487,13 @@
         <v>0.074609413743019104</v>
       </c>
       <c r="C26" s="2">
-        <v>-0.037770979106426239</v>
+        <v>-0.044249571859836578</v>
       </c>
       <c r="D26" s="2">
         <v>0.29864171147346497</v>
       </c>
       <c r="E26" s="2">
-        <v>0.19572587311267853</v>
+        <v>0.18453681468963623</v>
       </c>
     </row>
     <row r="27">
@@ -504,13 +504,13 @@
         <v>0.28229430317878723</v>
       </c>
       <c r="C27" s="2">
-        <v>0.18895919620990753</v>
+        <v>0.18111909925937653</v>
       </c>
       <c r="D27" s="2">
         <v>0.27642473578453064</v>
       </c>
       <c r="E27" s="2">
-        <v>0.16923424601554871</v>
+        <v>0.15645134449005127</v>
       </c>
     </row>
     <row r="28">
@@ -521,13 +521,13 @@
         <v>-0.0076445601880550385</v>
       </c>
       <c r="C28" s="2">
-        <v>-0.11057507991790771</v>
+        <v>-0.11490710824728012</v>
       </c>
       <c r="D28" s="2">
         <v>0.1967879980802536</v>
       </c>
       <c r="E28" s="2">
-        <v>0.084503613412380219</v>
+        <v>0.070952288806438446</v>
       </c>
     </row>
     <row r="29">
@@ -538,13 +538,13 @@
         <v>0.0766867995262146</v>
       </c>
       <c r="C29" s="2">
-        <v>-0.072416514158248901</v>
+        <v>-0.10546668618917465</v>
       </c>
       <c r="D29" s="2">
         <v>0.12130893766880035</v>
       </c>
       <c r="E29" s="2">
-        <v>0.0065942686051130295</v>
+        <v>-0.0076803639531135559</v>
       </c>
     </row>
     <row r="30">
@@ -555,13 +555,13 @@
         <v>-0.083214133977890015</v>
       </c>
       <c r="C30" s="2">
-        <v>-0.21749438345432281</v>
+        <v>-0.23613964021205902</v>
       </c>
       <c r="D30" s="2">
         <v>0.046730060130357742</v>
       </c>
       <c r="E30" s="2">
-        <v>-0.070078320801258087</v>
+        <v>-0.086243495345115662</v>
       </c>
     </row>
     <row r="31">
@@ -572,13 +572,13 @@
         <v>0.26412838697433472</v>
       </c>
       <c r="C31" s="2">
-        <v>0.14095918834209442</v>
+        <v>0.11797906458377838</v>
       </c>
       <c r="D31" s="2">
         <v>0.013340989127755165</v>
       </c>
       <c r="E31" s="2">
-        <v>-0.10176176577806473</v>
+        <v>-0.11882922798395157</v>
       </c>
     </row>
     <row r="32">
@@ -589,13 +589,13 @@
         <v>0.031572207808494568</v>
       </c>
       <c r="C32" s="2">
-        <v>-0.09456980973482132</v>
+        <v>-0.11242251098155975</v>
       </c>
       <c r="D32" s="2">
         <v>-0.026081738993525505</v>
       </c>
       <c r="E32" s="2">
-        <v>-0.14302507042884827</v>
+        <v>-0.16157659888267517</v>
       </c>
     </row>
     <row r="33">
@@ -606,13 +606,13 @@
         <v>-0.0335739366710186</v>
       </c>
       <c r="C33" s="2">
-        <v>-0.11952841281890869</v>
+        <v>-0.12870235741138458</v>
       </c>
       <c r="D33" s="2">
         <v>-0.036221664398908615</v>
       </c>
       <c r="E33" s="2">
-        <v>-0.15402337908744812</v>
+        <v>-0.17361731827259064</v>
       </c>
     </row>
     <row r="34">
@@ -623,13 +623,13 @@
         <v>-0.18428795039653778</v>
       </c>
       <c r="C34" s="2">
-        <v>-0.30826810002326965</v>
+        <v>-0.33340173959732056</v>
       </c>
       <c r="D34" s="2">
         <v>-0.074273541569709778</v>
       </c>
       <c r="E34" s="2">
-        <v>-0.19229646027088165</v>
+        <v>-0.21077050268650055</v>
       </c>
     </row>
     <row r="35">
@@ -640,13 +640,13 @@
         <v>-0.22589221596717834</v>
       </c>
       <c r="C35" s="2">
-        <v>-0.32292196154594421</v>
+        <v>-0.33752119541168213</v>
       </c>
       <c r="D35" s="2">
         <v>-0.062322854995727539</v>
       </c>
       <c r="E35" s="2">
-        <v>-0.17741735279560089</v>
+        <v>-0.1962914913892746</v>
       </c>
     </row>
     <row r="36">
@@ -657,13 +657,13 @@
         <v>-0.0725102499127388</v>
       </c>
       <c r="C36" s="2">
-        <v>-0.18241055309772491</v>
+        <v>-0.20360724627971649</v>
       </c>
       <c r="D36" s="2">
         <v>-0.11134803295135498</v>
       </c>
       <c r="E36" s="2">
-        <v>-0.2225511372089386</v>
+        <v>-0.23990306258201599</v>
       </c>
     </row>
     <row r="37">
@@ -674,13 +674,13 @@
         <v>-0.098903901875019073</v>
       </c>
       <c r="C37" s="2">
-        <v>-0.20955987274646759</v>
+        <v>-0.22327354550361633</v>
       </c>
       <c r="D37" s="2">
         <v>-0.099829010665416718</v>
       </c>
       <c r="E37" s="2">
-        <v>-0.21012218296527863</v>
+        <v>-0.22714321315288544</v>
       </c>
     </row>
     <row r="38">
@@ -691,13 +691,13 @@
         <v>-0.26578006148338318</v>
       </c>
       <c r="C38" s="2">
-        <v>-0.41687420010566711</v>
+        <v>-0.43984538316726685</v>
       </c>
       <c r="D38" s="2">
         <v>-0.10038943588733673</v>
       </c>
       <c r="E38" s="2">
-        <v>-0.218982994556427</v>
+        <v>-0.23799693584442139</v>
       </c>
     </row>
     <row r="39">
@@ -708,13 +708,13 @@
         <v>0.024342043325304985</v>
       </c>
       <c r="C39" s="2">
-        <v>-0.083582490682601929</v>
+        <v>-0.10582844913005829</v>
       </c>
       <c r="D39" s="2">
         <v>-0.072122864425182343</v>
       </c>
       <c r="E39" s="2">
-        <v>-0.18898722529411316</v>
+        <v>-0.20660831034183502</v>
       </c>
     </row>
     <row r="40">
@@ -725,13 +725,13 @@
         <v>-0.17709825932979584</v>
       </c>
       <c r="C40" s="2">
-        <v>-0.26524484157562256</v>
+        <v>-0.27452516555786133</v>
       </c>
       <c r="D40" s="2">
         <v>-0.038859359920024872</v>
       </c>
       <c r="E40" s="2">
-        <v>-0.15824517607688904</v>
+        <v>-0.1765500009059906</v>
       </c>
     </row>
     <row r="41">
@@ -742,13 +742,13 @@
         <v>0.13524341583251953</v>
       </c>
       <c r="C41" s="2">
-        <v>0.017290746793150902</v>
+        <v>0.0024161853361874819</v>
       </c>
       <c r="D41" s="2">
         <v>-0.028725698590278625</v>
       </c>
       <c r="E41" s="2">
-        <v>-0.14717511832714081</v>
+        <v>-0.16451279819011688</v>
       </c>
     </row>
     <row r="42">
@@ -759,13 +759,13 @@
         <v>-0.038617771118879318</v>
       </c>
       <c r="C42" s="2">
-        <v>-0.19927568733692169</v>
+        <v>-0.22638586163520813</v>
       </c>
       <c r="D42" s="2">
         <v>0.021272124722599983</v>
       </c>
       <c r="E42" s="2">
-        <v>-0.095496423542499542</v>
+        <v>-0.11245089024305344</v>
       </c>
     </row>
     <row r="43">
@@ -776,13 +776,13 @@
         <v>0.070111222565174103</v>
       </c>
       <c r="C43" s="2">
-        <v>-0.03830612450838089</v>
+        <v>-0.050904124975204468</v>
       </c>
       <c r="D43" s="2">
         <v>0.087257623672485352</v>
       </c>
       <c r="E43" s="2">
-        <v>-0.024876292794942856</v>
+        <v>-0.040518879890441895</v>
       </c>
     </row>
     <row r="44">
@@ -793,13 +793,13 @@
         <v>0.073479332029819489</v>
       </c>
       <c r="C44" s="2">
-        <v>-0.046243507415056229</v>
+        <v>-0.066996350884437561</v>
       </c>
       <c r="D44" s="2">
         <v>0.12403322011232376</v>
       </c>
       <c r="E44" s="2">
-        <v>0.011214782483875751</v>
+        <v>-0.0037897063884884119</v>
       </c>
     </row>
     <row r="45">
@@ -810,13 +810,13 @@
         <v>0.018692689016461372</v>
       </c>
       <c r="C45" s="2">
-        <v>-0.082780137658119202</v>
+        <v>-0.095272429287433624</v>
       </c>
       <c r="D45" s="2">
         <v>0.18320125341415405</v>
       </c>
       <c r="E45" s="2">
-        <v>0.069724157452583313</v>
+        <v>0.054440360516309738</v>
       </c>
     </row>
     <row r="46">
@@ -827,13 +827,13 @@
         <v>0.35107651352882385</v>
       </c>
       <c r="C46" s="2">
-        <v>0.25554844737052917</v>
+        <v>0.24528355896472931</v>
       </c>
       <c r="D46" s="2">
         <v>0.20146636664867401</v>
       </c>
       <c r="E46" s="2">
-        <v>0.085541516542434692</v>
+        <v>0.06933894008398056</v>
       </c>
     </row>
     <row r="47">
@@ -844,13 +844,13 @@
         <v>0.32808941602706909</v>
       </c>
       <c r="C47" s="2">
-        <v>0.21870696544647217</v>
+        <v>0.20754271745681763</v>
       </c>
       <c r="D47" s="2">
         <v>0.22309443354606628</v>
       </c>
       <c r="E47" s="2">
-        <v>0.11117653548717499</v>
+        <v>0.096680715680122375</v>
       </c>
     </row>
     <row r="48">
@@ -861,13 +861,13 @@
         <v>0.3553224503993988</v>
       </c>
       <c r="C48" s="2">
-        <v>0.24123717844486237</v>
+        <v>0.2247341126203537</v>
       </c>
       <c r="D48" s="2">
         <v>0.25815296173095703</v>
       </c>
       <c r="E48" s="2">
-        <v>0.13925060629844666</v>
+        <v>0.12323371320962906</v>
       </c>
     </row>
     <row r="49">
@@ -878,13 +878,13 @@
         <v>0.35541403293609619</v>
       </c>
       <c r="C49" s="2">
-        <v>0.26133951544761658</v>
+        <v>0.24954544007778168</v>
       </c>
       <c r="D49" s="2">
         <v>0.28363993763923645</v>
       </c>
       <c r="E49" s="2">
-        <v>0.16183334589004517</v>
+        <v>0.14526757597923279</v>
       </c>
     </row>
     <row r="50">
@@ -895,13 +895,13 @@
         <v>0.29962939023971558</v>
       </c>
       <c r="C50" s="2">
-        <v>0.15964698791503906</v>
+        <v>0.13650336861610413</v>
       </c>
       <c r="D50" s="2">
         <v>0.32331675291061401</v>
       </c>
       <c r="E50" s="2">
-        <v>0.1998257040977478</v>
+        <v>0.18186372518539429</v>
       </c>
     </row>
     <row r="51">
@@ -912,13 +912,13 @@
         <v>0.15603484213352203</v>
       </c>
       <c r="C51" s="2">
-        <v>0.031439471989870071</v>
+        <v>0.019690133631229401</v>
       </c>
       <c r="D51" s="2">
         <v>0.30520358681678772</v>
       </c>
       <c r="E51" s="2">
-        <v>0.17734892666339874</v>
+        <v>0.15794971585273743</v>
       </c>
     </row>
     <row r="52">
@@ -929,13 +929,13 @@
         <v>0.38563808798789978</v>
       </c>
       <c r="C52" s="2">
-        <v>0.21436057984828949</v>
+        <v>0.18807289004325867</v>
       </c>
       <c r="D52" s="2">
         <v>0.31449529528617859</v>
       </c>
       <c r="E52" s="2">
-        <v>0.18676285445690155</v>
+        <v>0.16635042428970337</v>
       </c>
     </row>
     <row r="53">
@@ -946,13 +946,13 @@
         <v>0.30286189913749695</v>
       </c>
       <c r="C53" s="2">
-        <v>0.15700110793113708</v>
+        <v>0.13130843639373779</v>
       </c>
       <c r="D53" s="2">
         <v>0.34667885303497314</v>
       </c>
       <c r="E53" s="2">
-        <v>0.21741728484630585</v>
+        <v>0.19608254730701447</v>
       </c>
     </row>
     <row r="54">
@@ -963,13 +963,13 @@
         <v>0.37578409910202026</v>
       </c>
       <c r="C54" s="2">
-        <v>0.25915110111236572</v>
+        <v>0.23409290611743927</v>
       </c>
       <c r="D54" s="2">
         <v>0.36161810159683228</v>
       </c>
       <c r="E54" s="2">
-        <v>0.2290860116481781</v>
+        <v>0.20640474557876587</v>
       </c>
     </row>
     <row r="55">
@@ -980,13 +980,13 @@
         <v>0.1880580335855484</v>
       </c>
       <c r="C55" s="2">
-        <v>0.053257469087839127</v>
+        <v>0.030057383701205254</v>
       </c>
       <c r="D55" s="2">
         <v>0.37769380211830139</v>
       </c>
       <c r="E55" s="2">
-        <v>0.24751675128936768</v>
+        <v>0.22515024244785309</v>
       </c>
     </row>
     <row r="56">
@@ -997,13 +997,13 @@
         <v>0.4117148220539093</v>
       </c>
       <c r="C56" s="2">
-        <v>0.30343231558799744</v>
+        <v>0.2831491231918335</v>
       </c>
       <c r="D56" s="2">
         <v>0.44006979465484619</v>
       </c>
       <c r="E56" s="2">
-        <v>0.31197571754455566</v>
+        <v>0.28785130381584167</v>
       </c>
     </row>
     <row r="57">
@@ -1014,13 +1014,13 @@
         <v>0.64497452974319458</v>
       </c>
       <c r="C57" s="2">
-        <v>0.51712703704833984</v>
+        <v>0.49232321977615356</v>
       </c>
       <c r="D57" s="2">
         <v>0.45727953314781189</v>
       </c>
       <c r="E57" s="2">
-        <v>0.3360971212387085</v>
+        <v>0.31205123662948608</v>
       </c>
     </row>
     <row r="58">
@@ -1031,13 +1031,13 @@
         <v>0.48986724019050598</v>
       </c>
       <c r="C58" s="2">
-        <v>0.36635807156562805</v>
+        <v>0.34244528412818909</v>
       </c>
       <c r="D58" s="2">
         <v>0.48500567674636841</v>
       </c>
       <c r="E58" s="2">
-        <v>0.36640718579292297</v>
+        <v>0.34300583600997925</v>
       </c>
     </row>
     <row r="59">
@@ -1048,13 +1048,13 @@
         <v>0.44431072473526001</v>
       </c>
       <c r="C59" s="2">
-        <v>0.32552364468574524</v>
+        <v>0.30521282553672791</v>
       </c>
       <c r="D59" s="2">
         <v>0.48190978169441223</v>
       </c>
       <c r="E59" s="2">
-        <v>0.36044332385063171</v>
+        <v>0.33636456727981567</v>
       </c>
     </row>
     <row r="60">
@@ -1065,13 +1065,13 @@
         <v>0.71741873025894165</v>
       </c>
       <c r="C60" s="2">
-        <v>0.61157023906707764</v>
+        <v>0.58399957418441772</v>
       </c>
       <c r="D60" s="2">
         <v>0.4954032301902771</v>
       </c>
       <c r="E60" s="2">
-        <v>0.37740015983581543</v>
+        <v>0.35436326265335083</v>
       </c>
     </row>
     <row r="61">
@@ -1082,13 +1082,13 @@
         <v>0.54052573442459106</v>
       </c>
       <c r="C61" s="2">
-        <v>0.43145304918289185</v>
+        <v>0.40587228536605835</v>
       </c>
       <c r="D61" s="2">
-        <v>0.50586426258087158</v>
+        <v>0.50883108377456665</v>
       </c>
       <c r="E61" s="2">
-        <v>0.38664612174034119</v>
+        <v>0.36279836297035217</v>
       </c>
     </row>
     <row r="62">
@@ -1099,13 +1099,13 @@
         <v>0.55239719152450562</v>
       </c>
       <c r="C62" s="2">
-        <v>0.42979174852371216</v>
+        <v>0.40989997982978821</v>
       </c>
       <c r="D62" s="2">
-        <v>0.48599138855934143</v>
+        <v>0.50371700525283813</v>
       </c>
       <c r="E62" s="2">
-        <v>0.36800599098205566</v>
+        <v>0.35645678639411926</v>
       </c>
     </row>
     <row r="63">
@@ -1116,13 +1116,13 @@
         <v>0.34792107343673706</v>
       </c>
       <c r="C63" s="2">
-        <v>0.20547620952129364</v>
+        <v>0.17432132363319397</v>
       </c>
       <c r="D63" s="2">
-        <v>0.48534542322158813</v>
+        <v>0.53642499446868896</v>
       </c>
       <c r="E63" s="2">
-        <v>0.36828064918518066</v>
+        <v>0.3900296688079834</v>
       </c>
     </row>
     <row r="64">
@@ -1133,23 +1133,176 @@
         <v>0.30949902534484863</v>
       </c>
       <c r="C64" s="2">
-        <v>0.20586903393268585</v>
+        <v>0.19204583764076233</v>
       </c>
       <c r="D64" s="2">
-        <v>0.49355235695838928</v>
+        <v>0.54930287599563599</v>
       </c>
       <c r="E64" s="2">
-        <v>0.37683206796646118</v>
+        <v>0.40778085589408875</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1">
         <v>45748</v>
       </c>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
+      <c r="B65" s="2">
+        <v>0.53256571292877197</v>
+      </c>
+      <c r="C65" s="2">
+        <v>0.35906502604484558</v>
+      </c>
+      <c r="D65" s="2">
+        <v>0.50675815343856812</v>
+      </c>
+      <c r="E65" s="2">
+        <v>0.36841088533401489</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B66" s="2">
+        <v>0.59894782304763794</v>
+      </c>
+      <c r="C66" s="2">
+        <v>0.43524903059005737</v>
+      </c>
+      <c r="D66" s="2">
+        <v>0.48829907178878784</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0.35630831122398376</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B67" s="2">
+        <v>0.78423887491226196</v>
+      </c>
+      <c r="C67" s="2">
+        <v>0.64460116624832153</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0.47609299421310425</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0.3487638533115387</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B68" s="2">
+        <v>0.56021183729171753</v>
+      </c>
+      <c r="C68" s="2">
+        <v>0.46497336030006409</v>
+      </c>
+      <c r="D68" s="2">
+        <v>0.49794811010360718</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0.3820652961730957</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B69" s="2">
+        <v>0.33451622724533081</v>
+      </c>
+      <c r="C69" s="2">
+        <v>0.22967007756233215</v>
+      </c>
+      <c r="D69" s="2">
+        <v>0.54828548431396484</v>
+      </c>
+      <c r="E69" s="2">
+        <v>0.43423295021057129</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B70" s="2">
+        <v>0.37439388036727905</v>
+      </c>
+      <c r="C70" s="2">
+        <v>0.29694893956184387</v>
+      </c>
+      <c r="D70" s="2">
+        <v>0.55025047063827515</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0.4436289370059967</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B71" s="2">
+        <v>0.44254240393638611</v>
+      </c>
+      <c r="C71" s="2">
+        <v>0.34199985861778259</v>
+      </c>
+      <c r="D71" s="2">
+        <v>0.54329365491867065</v>
+      </c>
+      <c r="E71" s="2">
+        <v>0.44482606649398804</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B72" s="2">
+        <v>0.54461711645126343</v>
+      </c>
+      <c r="C72" s="2">
+        <v>0.47403445839881897</v>
+      </c>
+      <c r="D72" s="2">
+        <v>0.50313615798950195</v>
+      </c>
+      <c r="E72" s="2">
+        <v>0.41153019666671753</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B73" s="2">
+        <v>0.76253539323806763</v>
+      </c>
+      <c r="C73" s="2">
+        <v>0.66155457496643066</v>
+      </c>
+      <c r="D73" s="2">
+        <v>0.49172100424766541</v>
+      </c>
+      <c r="E73" s="2">
+        <v>0.40084159374237061</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
     </row>
   </sheetData>
 </worksheet>
